--- a/DemonstratorSchrittmotor/author.xlsx
+++ b/DemonstratorSchrittmotor/author.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hanna\Documents\GitHub\Handbuch\LaTeXTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perew\OneDrive\Dokumente\Handbuch\DemonstratorSchrittmotor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CD619B-8468-4432-9715-16FE0D0F29BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F80C853-4EB3-4000-A9B2-76968F3D27DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export Summary" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="76">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -187,9 +187,6 @@
     <t>In diesem Projekt wurde mittels eines Arduino Nano 33 BLE Sense die Ansteuerung eines Schrittmotors an einem CNC-Tisch umgesetzt. Der Schrittmotor wird mithilfe eines Treibers angesteuert und kann über die Bedienelemente in verschiedenen Geschwindigkeitsstufen betrieben werden. Des Weiteren ist ein Geschwindigkeitssensor Typ LM393 verbaut, mit dem die tatsächliche Geschwindigkeit des Schrittmotors gemessen werden kann.</t>
   </si>
   <si>
-    <t>LINK GITHUB HIER EINFÜGEN</t>
-  </si>
-  <si>
     <t>Hannah</t>
   </si>
   <si>
@@ -232,20 +229,6 @@
     <t>Crety</t>
   </si>
   <si>
-    <r>
-      <t>7024</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>xxx</t>
-    </r>
-  </si>
-  <si>
     <t>kthxjessy</t>
   </si>
   <si>
@@ -258,9 +241,6 @@
     <t>&lt;Fachbereich Technik&gt;</t>
   </si>
   <si>
-    <t>xxxxxx</t>
-  </si>
-  <si>
     <t>chantal.crety@stud.hs-emden-leer.de</t>
   </si>
   <si>
@@ -274,13 +254,19 @@
   </si>
   <si>
     <t>16.06.2000</t>
+  </si>
+  <si>
+    <t>chantalcrety@web.de</t>
+  </si>
+  <si>
+    <t>https://github.com/chanti-logic/Handbuch</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -340,20 +326,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -417,7 +390,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -448,14 +421,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -472,6 +443,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -1611,11 +1583,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
     </row>
     <row r="7" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -1719,11 +1691,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="61.9" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
     </row>
@@ -1751,11 +1723,11 @@
       <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
     </row>
@@ -1769,8 +1741,8 @@
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
-        <v>51</v>
+      <c r="A7" s="28" t="s">
+        <v>75</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -1804,7 +1776,7 @@
     <mergeCell ref="A5:C5"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A7" r:id="rId1" display="ML24-04 Keyword Spotting with an Arduino Nano 33 BLE Sense" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="A7" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740200000000005" bottom="0.78740200000000005" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -1824,7 +1796,8 @@
     <col min="3" max="3" width="33.140625" style="5" customWidth="1"/>
     <col min="4" max="4" width="16.140625" style="5" customWidth="1"/>
     <col min="5" max="5" width="43.85546875" style="5" customWidth="1"/>
-    <col min="6" max="7" width="8.85546875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="5" customWidth="1"/>
     <col min="8" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
@@ -1862,7 +1835,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>13</v>
@@ -1876,22 +1849,22 @@
     </row>
     <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>52</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>53</v>
       </c>
       <c r="C5" s="10">
         <v>7024688</v>
       </c>
       <c r="D5" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="F5" s="17" t="s">
         <v>56</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1915,7 +1888,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -1987,7 +1960,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -2027,7 +2000,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -2420,22 +2393,22 @@
     </row>
     <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>62</v>
       </c>
       <c r="C5" s="18">
         <v>7024880</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2459,7 +2432,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -2531,7 +2504,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -2570,8 +2543,8 @@
       <c r="A19" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="23" t="s">
-        <v>75</v>
+      <c r="B19" s="21" t="s">
+        <v>72</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -2629,7 +2602,7 @@
         <v>26</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -2639,7 +2612,7 @@
     <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
@@ -2911,7 +2884,8 @@
     <col min="3" max="3" width="15.42578125" style="5" customWidth="1"/>
     <col min="4" max="4" width="16.140625" style="5" customWidth="1"/>
     <col min="5" max="5" width="39.28515625" style="5" customWidth="1"/>
-    <col min="6" max="7" width="11.42578125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="5" customWidth="1"/>
     <col min="8" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
@@ -2963,22 +2937,22 @@
     </row>
     <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>66</v>
+      <c r="C5" s="18">
+        <v>7025255</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>71</v>
+        <v>69</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3002,7 +2976,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -3074,7 +3048,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -3086,7 +3060,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -3113,8 +3087,8 @@
       <c r="A19" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="23" t="s">
-        <v>76</v>
+      <c r="B19" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -3172,7 +3146,7 @@
         <v>26</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -3182,7 +3156,7 @@
     <row r="26" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
@@ -3434,9 +3408,10 @@
   <hyperlinks>
     <hyperlink ref="B40" r:id="rId1" xr:uid="{D3CE74DB-3372-4D8E-8038-3ACB444024CD}"/>
     <hyperlink ref="E5" r:id="rId2" xr:uid="{D4630012-1892-431F-AA1D-FF1C1B9B5231}"/>
+    <hyperlink ref="F5" r:id="rId3" xr:uid="{C448856C-A5BC-41BB-ABFC-97C25D3D401D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740200000000005" bottom="0.78740200000000005" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
